--- a/data/input/Planning for Timetable.xlsx
+++ b/data/input/Planning for Timetable.xlsx
@@ -16,9 +16,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Teacher load table with subject" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Centre Room Allocation" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Teacher Availability" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Net Teachers" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <externalReferences>
-    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
+    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId12"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Class list answer'!$A$1:$L$109</definedName>
@@ -7363,6 +7364,41 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Teacher Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Mr. Peter Barrett</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Mr. Chris Hon</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/input/Planning for Timetable.xlsx
+++ b/data/input/Planning for Timetable.xlsx
@@ -17,9 +17,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Centre Room Allocation" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Teacher Availability" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Net Teachers" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="English Weekly" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <externalReferences>
-    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId12"/>
+    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId13"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Class list answer'!$A$1:$L$109</definedName>
@@ -31,7 +32,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="26">
+  <fonts count="28">
     <font>
       <name val="新細明體"/>
       <charset val="136"/>
@@ -196,8 +197,16 @@
       <i val="1"/>
       <color rgb="006B7280"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00888888"/>
+    </font>
   </fonts>
-  <fills count="21">
+  <fills count="22">
     <fill>
       <patternFill/>
     </fill>
@@ -313,6 +322,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
   </fills>
@@ -881,7 +895,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="271">
+  <cellXfs count="273">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1651,6 +1665,10 @@
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -7374,23 +7392,1015 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>Teacher Name</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="24" t="inlineStr">
         <is>
           <t>Mr. Peter Barrett</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>Mr. Chris Hon</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" style="263" min="1" max="1"/>
+    <col width="20" customWidth="1" style="263" min="2" max="2"/>
+    <col width="20" customWidth="1" style="263" min="3" max="3"/>
+    <col width="20" customWidth="1" style="263" min="4" max="4"/>
+    <col width="20" customWidth="1" style="263" min="5" max="5"/>
+    <col width="20" customWidth="1" style="263" min="6" max="6"/>
+    <col width="20" customWidth="1" style="263" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="271" t="inlineStr">
+        <is>
+          <t>Class Code</t>
+        </is>
+      </c>
+      <c r="B1" s="271" t="inlineStr">
+        <is>
+          <t>T2025C wk1-5</t>
+        </is>
+      </c>
+      <c r="C1" s="271" t="inlineStr">
+        <is>
+          <t>T2025C wk6-10</t>
+        </is>
+      </c>
+      <c r="D1" s="271" t="inlineStr">
+        <is>
+          <t>T2025C wk11-15</t>
+        </is>
+      </c>
+      <c r="E1" s="271" t="inlineStr">
+        <is>
+          <t>T2026A wk1-5</t>
+        </is>
+      </c>
+      <c r="F1" s="271" t="inlineStr">
+        <is>
+          <t>T2026A wk6-10</t>
+        </is>
+      </c>
+      <c r="G1" s="271" t="inlineStr">
+        <is>
+          <t>T2026A wk11-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="272" t="inlineStr">
+        <is>
+          <t># Edit teacher names below. System uses this sheet if filled; otherwise uses built-in defaults.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>DAE102_CS1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Mr. Ivan Yuen</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Mr. Ivan Yuen</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Mr. Ivan Yuen</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Mr. Ivan Yuen</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Mr. Peter Barrett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Mr. Ivan Yuen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>DAE102_CS2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Mr. Ivan Yuen</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Mr. Ivan Yuen</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Mr. Ivan Yuen</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Mr. Ivan Yuen</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mr. Peter Barrett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Mr. Ivan Yuen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DAE102_CS3</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Mr. Ivan Yuen</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Mr. Ivan Yuen</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Mr. Ivan Yuen</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Mr. Ivan Yuen</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mr. Peter Barrett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Mr. Ivan Yuen</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>DAE102_CS4</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ms. Elise Ye</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>Mr. Chris Hon</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Ms. Cherry Ip</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Ms. Elise Ye</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mr. Chris Hon</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ms. Cherry Ip</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>DAE102_CS5</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ms. Elise Ye</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Mr. Chris Hon</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Ms. Cherry Ip</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Ms. Elise Ye</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mr. Chris Hon</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Ms. Cherry Ip</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>DAE102_CS6</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Mr. Chris Hon</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ms. Cherry Ip</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Mr. Ray Leung</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Mr. Chris Hon</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ms. Cherry Ip</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Mr. Ray Leung</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>DAE102_CS7</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Mr. Ivan Yuen</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Mr. Ivan Yuen</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Mr. Ivan Yuen</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Mr. Ivan Yuen</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mr. Peter Barrett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Mr. Ivan Yuen</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DAE102_WT1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ms. Cherry Ip</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ms. Cherry Ip</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Mr. Chris Hon</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Ms. Cherry Ip</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ms. Cherry Ip</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Mr. Chris Hon</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>DAE102_WT2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ms. Cherry Ip</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ms. Cherry Ip</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Mr. Chris Hon</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Ms. Cherry Ip</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ms. Cherry Ip</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Mr. Chris Hon</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>DAE102_SW1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Mr. Chris Hon</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Mr. Chris Hon</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Ms. Cherry Ip</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Mr. Chris Hon</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mr. Chris Hon</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Ms. Cherry Ip</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>DAE102_TW1</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Mr. Chris Hon</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ms. Elise Ye</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Ms. Sasha Cheung</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Mr. Chris Hon</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ms. Elise Ye</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Ms. Sasha Cheung</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>DAE102_TW2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Mr. Chris Hon</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ms. Elise Ye</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Ms. Sasha Cheung</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Mr. Chris Hon</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ms. Elise Ye</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Ms. Sasha Cheung</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>DAE102_TW3</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Mr. Chris Hon</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ms. Cherry Ip</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Mr. Ray Leung</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Mr. Chris Hon</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ms. Cherry Ip</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Mr. Ray Leung</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>DAE102_TM1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ms. Sasha Cheung</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ms. Sasha Cheung</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Mr. Peter Barrett</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Ms. Sasha Cheung</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Ms. Sasha Cheung</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Mr. Peter Barrett</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>DAE102_TM2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ms. Sasha Cheung</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ms. Sasha Cheung</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Mr. Peter Barrett</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Ms. Sasha Cheung</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ms. Sasha Cheung</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Mr. Peter Barrett</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>DAE102_TM3</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ms. Sasha Cheung</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ms. Sasha Cheung</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Mr. Peter Barrett</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Ms. Sasha Cheung</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Ms. Sasha Cheung</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Mr. Peter Barrett</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>DAE102_TM4</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ms. Sasha Cheung</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ms. Sasha Cheung</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Mr. Peter Barrett</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Ms. Sasha Cheung</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ms. Sasha Cheung</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Mr. Peter Barrett</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>DAE102_KT1</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ms. Cherry Ip</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ms. Cherry Ip</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Mr. Chris Hon</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Ms. Cherry Ip</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Ms. Cherry Ip</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Mr. Chris Hon</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>DAE102_KT2</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ms. Cherry Ip</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ms. Cherry Ip</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Mr. Chris Hon</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Ms. Cherry Ip</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ms. Cherry Ip</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Mr. Chris Hon</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>DAE102_KT3</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ms. Cherry Ip</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Mr. Chris Hon</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Ms. Cherry Ip</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Ms. Cherry Ip</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mr. Chris Hon</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Ms. Cherry Ip</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>DAE102_TK1</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ms. Cherry Ip</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Mr. Chris Hon</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Ms. Cherry Ip</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Ms. Cherry Ip</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Mr. Chris Hon</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Ms. Cherry Ip</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>DAE102_ST1</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ms. Lee Kit Wan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Mr. Peter Barrett</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Ms. Lee Kit Wan</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Mr. Peter Barrett</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Ms. Lee Kit Wan</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Ms. Lee Kit Wan</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>DAE102_ST2</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Mr. Peter Barrett</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ms. Elise Ye</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Ms. Elise Ye</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Mr. Peter Barrett</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ms. Elise Ye</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Ms. Elise Ye</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>DAE102_ST3</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Mr. Peter Barrett</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ms. Elise Ye</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Ms. Elise Ye</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Mr. Peter Barrett</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Ms. Elise Ye</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Ms. Elise Ye</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>DAE102_FL1</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Ms. Lee Kit Wan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Mr. Peter Barrett</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Ms. Lee Kit Wan</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Mr. Chris Hon</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Ms. Lee Kit Wan</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Ms. Lee Kit Wan</t>
         </is>
       </c>
     </row>
